--- a/data/trans_dic/P3A$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,38; 50,16</t>
+          <t>41,01; 50,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 23,85</t>
+          <t>16,39; 23,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,71; 35,31</t>
+          <t>28,0; 35,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,97; 51,16</t>
+          <t>19,9; 51,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,53; 27,41</t>
+          <t>22,65; 27,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,63; 37,95</t>
+          <t>22,23; 37,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45,59; 54,61</t>
+          <t>46,21; 55,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 25,04</t>
+          <t>9,51; 24,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 37,78</t>
+          <t>21,96; 38,01</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,46; 50,77</t>
+          <t>43,74; 50,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 20,81</t>
+          <t>14,76; 20,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,23; 33,73</t>
+          <t>27,87; 33,77</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,93; 49,08</t>
+          <t>34,48; 49,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,55</t>
+          <t>16,55; 22,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,08; 34,81</t>
+          <t>28,13; 34,76</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>262779; 318501</t>
+          <t>260394; 318264</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118536; 172984</t>
+          <t>118851; 171940</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>390554; 480274</t>
+          <t>380843; 480453</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>262095; 610232</t>
+          <t>237376; 609670</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>216020; 262738</t>
+          <t>217128; 262583</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>486966; 816404</t>
+          <t>478250; 816366</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>321269; 384811</t>
+          <t>325665; 387721</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95578; 233692</t>
+          <t>88730; 232674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>357419; 618868</t>
+          <t>359697; 622696</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>402490; 470256</t>
+          <t>405121; 471841</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161555; 227602</t>
+          <t>161415; 227891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570215; 681340</t>
+          <t>562910; 682187</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1208113; 1697451</t>
+          <t>1192592; 1700703</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>627449; 836915</t>
+          <t>614292; 843229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2013590; 2495759</t>
+          <t>2016671; 2492035</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$pareja-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,01; 50,12</t>
+          <t>43,01; 51,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,39; 23,71</t>
+          <t>19,7; 24,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,0; 35,32</t>
+          <t>31,72; 36,42</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 51,11</t>
+          <t>47,17; 54,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,65; 27,39</t>
+          <t>21,72; 26,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,23; 37,94</t>
+          <t>35,29; 39,58</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46,21; 55,02</t>
+          <t>46,85; 55,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 24,93</t>
+          <t>21,43; 26,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,96; 38,01</t>
+          <t>34,98; 39,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,74; 50,94</t>
+          <t>44,01; 50,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 20,84</t>
+          <t>17,38; 21,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 33,77</t>
+          <t>30,42; 34,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,17</t>
+          <t>47,17; 50,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,72</t>
+          <t>21,06; 23,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,13; 34,76</t>
+          <t>34,2; 36,53</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>289092</t>
+          <t>325098</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152102</t>
+          <t>161405</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441194</t>
+          <t>486503</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>260394; 318264</t>
+          <t>296891; 353767</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>118851; 171940</t>
+          <t>144608; 180408</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>380843; 480453</t>
+          <t>451802; 518767</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>473828</t>
+          <t>534023</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>239285</t>
+          <t>258177</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713113</t>
+          <t>792200</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>237376; 609670</t>
+          <t>494795; 568768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>217128; 262583</t>
+          <t>232701; 281594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>478250; 816366</t>
+          <t>748190; 839179</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>354950</t>
+          <t>410497</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>173422</t>
+          <t>195711</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528372</t>
+          <t>606208</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>325665; 387721</t>
+          <t>376273; 442725</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88730; 232674</t>
+          <t>174042; 219005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>359697; 622696</t>
+          <t>565089; 643033</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>437081</t>
+          <t>468500</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>200961</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638042</t>
+          <t>684546</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>405121; 471841</t>
+          <t>435428; 503136</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161415; 227891</t>
+          <t>194287; 239097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>562910; 682187</t>
+          <t>641048; 727176</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1192592; 1700703</t>
+          <t>1665820; 1796052</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>614292; 843229</t>
+          <t>786819; 873757</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2016671; 2492035</t>
+          <t>2485627; 2654563</t>
         </is>
       </c>
     </row>
